--- a/black-friday-categoria-c/BLACK_FRIDAY_PROPUESTA_CATEGORIA_C.xlsx
+++ b/black-friday-categoria-c/BLACK_FRIDAY_PROPUESTA_CATEGORIA_C.xlsx
@@ -59,7 +59,7 @@
     <t>excluidos</t>
   </si>
   <si>
-    <t>2026-09-28T05:43:53.571611+00:00</t>
+    <t>2026-09-28T05:44:10.357448+00:00</t>
   </si>
   <si>
     <t>Octubre 2025 → Septiembre 2026</t>

--- a/black-friday-categoria-c/BLACK_FRIDAY_PROPUESTA_CATEGORIA_C.xlsx
+++ b/black-friday-categoria-c/BLACK_FRIDAY_PROPUESTA_CATEGORIA_C.xlsx
@@ -59,7 +59,7 @@
     <t>excluidos</t>
   </si>
   <si>
-    <t>2026-09-28T12:10:22.242388+00:00</t>
+    <t>2026-09-28T12:15:39.454737+00:00</t>
   </si>
   <si>
     <t>Octubre 2025 → Septiembre 2026</t>

--- a/black-friday-categoria-c/BLACK_FRIDAY_PROPUESTA_CATEGORIA_C.xlsx
+++ b/black-friday-categoria-c/BLACK_FRIDAY_PROPUESTA_CATEGORIA_C.xlsx
@@ -59,7 +59,7 @@
     <t>excluidos</t>
   </si>
   <si>
-    <t>2026-09-28T12:15:39.454737+00:00</t>
+    <t>2026-09-28T12:19:30.365243+00:00</t>
   </si>
   <si>
     <t>Octubre 2025 → Septiembre 2026</t>
